--- a/supplemental/reflectance_vs_wavelength/reflectance_vs_wavelength_summary.xlsx
+++ b/supplemental/reflectance_vs_wavelength/reflectance_vs_wavelength_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakep\Documents\Optics_local\UofA\bsdf-tools\supplemental\reflectance_vs_wavelength\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF0C507-85E0-4084-B6E5-439336C53F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B37EB33-4154-4A5C-9733-F780E261C2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3468" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>DEEP SPACE BLACK - Full Spectrum Basic</t>
   </si>
   <si>
-    <t>Aeroglaze 9924 Primer with Aeroglaze 2307 Black</t>
-  </si>
-  <si>
     <t>Vacuum Black on Aluminum</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>(approx., ~ +/- 0.5 mm maybe)</t>
+  </si>
+  <si>
+    <t>Aeroglaze 9924 Primer with Aeroglaze Z307 Black</t>
   </si>
 </sst>
 </file>
@@ -588,71 +588,71 @@
   <sheetData>
     <row r="2" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="1"/>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>11</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>12</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C6" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -661,52 +661,52 @@
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C12" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C13" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C14" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -716,14 +716,14 @@
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2"/>
     </row>
